--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70294B4D-FB7C-4D51-821A-A729B6D20ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357A721C-24FB-4FFF-85FB-6AD1D4CDCFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -1815,16 +1815,12 @@
   </si>
   <si>
     <t>社会を支えるITサービス</t>
-    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2464,10 +2460,10 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2853,7 +2849,7 @@
       <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8769,16 +8765,15 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
-        <f t="shared" ref="A2" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>584</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>46266</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>46278</v>
       </c>
     </row>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357A721C-24FB-4FFF-85FB-6AD1D4CDCFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FD0F16-0D74-4962-908F-ADE1BA1B44FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
+    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
   <sheets>
     <sheet name="受講生一覧" sheetId="3" r:id="rId1"/>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAE4BD0-E3B3-445F-A3B5-7E091557C86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B414AD25-EBE6-4E6E-A0A3-5925847BB000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>社会を支えるITサービス</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
   <si>
     <t>gagag</t>
     <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>社会を支えるITサービd</t>
   </si>
 </sst>
 </file>
@@ -1147,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3">
         <v>46266</v>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B414AD25-EBE6-4E6E-A0A3-5925847BB000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D5B34A-77DA-4B2A-9A36-7A3D6A9F5661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -104,12 +104,41 @@
   </si>
   <si>
     <t>社会を支えるITサービd</t>
+  </si>
+  <si>
+    <t>除外日-開始</t>
+    <rPh sb="0" eb="2">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>除外日-終了</t>
+    <rPh sb="0" eb="2">
+      <t>ジョガイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -742,7 +771,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,6 +782,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1112,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7305DA-9532-48D5-A9AB-D0B7DDD41B28}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="34.69921875" bestFit="1" customWidth="1"/>
@@ -1120,9 +1155,11 @@
     <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.19921875" customWidth="1"/>
     <col min="6" max="6" width="30.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.296875" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1141,8 +1178,14 @@
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1160,6 +1203,12 @@
       </c>
       <c r="F2" t="b">
         <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>46266</v>
+      </c>
+      <c r="H2" s="5">
+        <v>46266</v>
       </c>
     </row>
   </sheetData>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D5B34A-77DA-4B2A-9A36-7A3D6A9F5661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8CA90D-1969-4C12-9C54-C32A0ED888BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
@@ -92,14 +92,7 @@
     <t>a</t>
   </si>
   <si>
-    <t>gagaga</t>
-  </si>
-  <si>
     <t>L01</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>gagag</t>
     <phoneticPr fontId="18"/>
   </si>
   <si>
@@ -129,6 +122,18 @@
     <rPh sb="4" eb="6">
       <t>シュウリョウ</t>
     </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>L02</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>a</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1147,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7305DA-9532-48D5-A9AB-D0B7DDD41B28}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="34.69921875" bestFit="1" customWidth="1"/>
@@ -1179,10 +1184,10 @@
         <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -1193,13 +1198,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1209,6 +1214,26 @@
       </c>
       <c r="H2" s="5">
         <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1246,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3">
         <v>46266</v>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8CA90D-1969-4C12-9C54-C32A0ED888BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E2AFD4-C428-4672-BAAA-C7BA5592A492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>社会を支えるITサービd</t>
-  </si>
-  <si>
     <t>除外日-開始</t>
     <rPh sb="0" eb="2">
       <t>ジョガイ</t>
@@ -135,6 +132,9 @@
   <si>
     <t>a</t>
     <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>社会を支えるITサービス</t>
   </si>
 </sst>
 </file>
@@ -1184,10 +1184,10 @@
         <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -1198,10 +1198,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1224,13 +1224,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3">
         <v>46266</v>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E2AFD4-C428-4672-BAAA-C7BA5592A492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A07413-A6F1-4F0F-8F73-D0E6229ADD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>

--- a/tool/kintone-aggregator/clients/地域共催.xlsx
+++ b/tool/kintone-aggregator/clients/地域共催.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\clients\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A07413-A6F1-4F0F-8F73-D0E6229ADD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D36D829-4371-4A28-8EB7-C87AED7FB8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A5261433-3D19-4214-B99D-71C409BE4618}"/>
   </bookViews>
   <sheets>
     <sheet name="受講生一覧" sheetId="3" r:id="rId1"/>
@@ -780,20 +780,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -1159,35 +1159,35 @@
     <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.19921875" customWidth="1"/>
-    <col min="6" max="6" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="5" customWidth="1"/>
-    <col min="8" max="8" width="16.296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -1206,14 +1206,14 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="b">
+      <c r="F2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46266</v>
+      </c>
+      <c r="H2" t="b">
         <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>46266</v>
-      </c>
-      <c r="H2" s="5">
-        <v>46266</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
@@ -1232,7 +1232,7 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="b">
+      <c r="H3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1253,16 +1253,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1273,10 +1273,10 @@
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <v>46266</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>46278</v>
       </c>
     </row>
